--- a/data/자주묻는질문.xlsx
+++ b/data/자주묻는질문.xlsx
@@ -1031,7 +1031,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>기초연금 수급자를 대상으로 하며, 매년 12월 초에 모집하고 연중 수시로 추가모집(대기자 등록)합니다. 담당자에게 전화로 먼저 문의하신 후 방문 상담해 주세요.</t>
+          <t>기초연금 수급자를 대상으로 하며, 매년 12월 초에 모집하고 연중 수시로 추가모집(대기자 등록)합니다. 노인일자리 담당자(033-747-3636)에게 전화로 먼저 문의하신 후 방문 상담해 주세요.</t>
         </is>
       </c>
     </row>
